--- a/www/download/IND.gross_output.s.du.zdW16.xlsx
+++ b/www/download/IND.gross_output.s.du.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>166243.364398724</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>158686.532684341</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>167854.430990904</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>195348.994064941</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>225318.2009049</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>249190.770842704</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>270386.674865912</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>323376.995430295</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>353205.496073993</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>323995.612197441</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>370479.160079084</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>447237.87864779</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>430819.607843062</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>430794.490386772</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>424043.379833747</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>65292.2622495001</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>63924.5567610929</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>61661.4656091667</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>69869.7357871344</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>78135.0838456573</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>82149.8411027971</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>90704.3170767123</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>103912.273758827</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>116464.679457349</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>101146.592115722</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>116935.931121601</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>137662.23763856</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>134453.864992367</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>139366.499909021</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130719.412943404</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>83788.2240435774</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>79624.5002341333</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>78195.1609644261</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>90615.4327112397</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>106958.65283709</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>111613.571195993</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>128492.998657004</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>153479.995030091</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>172492.894367896</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>145147.059642189</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>181450.472756233</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>227017.492174369</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>203399.929905918</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>200610.382101562</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219833.303258427</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>54936.7178041274</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>53763.3023890589</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54022.6873301387</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>58713.9867794457</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67047.4611363596</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70846.8036169951</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79256.7138976847</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>91877.7566753506</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104375.951871024</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>87915.9625207093</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>86362.2298400822</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>92901.0633363677</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>86913.6648468647</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>86865.3474258383</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93348.7167444494</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1314398.4627657</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1257763.98919715</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1313229.65075114</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1472172.48951633</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1701349.53266848</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.898</t>
+          <t>1880651.94982977</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1959727.70284529</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2222939.16428745</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.539</t>
+          <t>2513909.62497538</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t>2178951.00493152</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2480274.46065065</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>2666684.83507392</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>2570407.22723283</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>2594130.06187361</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.617</t>
+          <t>2617034.11689383</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>225400.453368331</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>216953.649327893</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>218837.920968687</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>249356.419979942</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>288382.000770862</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>310385.126836333</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>334762.994059109</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>367852.756218874</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>402591.42507577</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>347073.016776246</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>412320.871574428</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>474234.428427107</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>472456.576917089</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>450188.754343489</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>461225.322046267</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16.828</t>
+          <t>16903054.9779685</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16.319</t>
+          <t>16440231.964279</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.418</t>
+          <t>16636219.1083225</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.292</t>
+          <t>18569601.9558345</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21216456.6564582</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.602</t>
+          <t>23892990.9433805</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26.832</t>
+          <t>27232830.1592678</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>31.529</t>
+          <t>31976036.7728741</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36.369</t>
+          <t>36668923.2773928</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>35.153</t>
+          <t>35183455.1650332</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>38.363</t>
+          <t>38572104.8517201</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>45.261</t>
+          <t>45392672.7970682</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>45.721</t>
+          <t>45492964.064684</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>46.337</t>
+          <t>45709903.1242978</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>44.994</t>
+          <t>44994162.7152157</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4328.95645645455</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5032.5666148303</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5641.09633512545</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6560.77171736665</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6529.08939335952</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6902.50160066777</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6659.72930286072</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7894.15473443603</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10285.5254765527</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8051.40847152857</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8137.20342943388</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8484.97564646326</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7458.05213985746</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7082.784174137</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6926.77682516163</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>87563.7987000966</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>83522.2962190524</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>84448.2833355864</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>92832.4703115953</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>105353.460967137</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>116037.114751144</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>126850.082089094</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>147064.010431385</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>161321.4563975</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>131292.84663333</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>150877.84335388</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>173355.03177668</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>159699.835554396</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>162765.041921846</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164067.273101219</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>582761.303531784</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>549177.127272767</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>532160.210762653</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>605258.316092798</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>680191.946314986</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>731175.647720332</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>819725.41198056</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>954220.151200086</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1036498.5895378</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>848860.909825268</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>987007.239057392</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1154526.24276837</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1071026.63820939</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1076013.3701997</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1063269.33224329</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>49245.8375578247</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>49555.4577036248</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>50415.7189074535</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>59339.2877822353</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>66697.9542314488</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>72889.175135079</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>71268.6651274699</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>85640.1904062427</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>97495.4427420289</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>78005.914411483</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>78934.6455353159</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>87674.0244512433</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>84909.1995992714</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>90189.7505540904</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86666.5789308668</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>307760.362478858</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>308727.831513169</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>332070.008387953</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>370873.91980336</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>426328.918396477</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>478057.993577063</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>533421.79557042</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>609893.627316639</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>655649.87308514</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>494119.322785353</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>574534.917332565</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>647963.709798344</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>597030.860868283</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>570750.973103413</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580821.509349322</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10772.0160704543</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10504.8746419326</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11451.2373772179</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13304.9594207036</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14536.4689750434</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15761.6665464105</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18572.2799951684</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20394.9175270408</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21767.9545208192</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15254.1178847484</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16706.0147998885</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21593.3910002515</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20182.8260225721</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19443.6326971038</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20445.2139607153</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>52274.907670431</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>49522.9575656529</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>50479.2078778153</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>58325.0692867936</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>66471.7108169259</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>72909.3475756334</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>79446.4510733909</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>90395.4883898141</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>106548.853727212</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>72921.6440489654</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>82142.1821451011</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>91944.6064126641</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>86865.9011554446</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>83843.9540047393</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81600.9509580447</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>369133.845094147</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>357394.063847349</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>351689.612475544</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>395614.473189462</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>466872.62575884</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>504296.129642881</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>543478.164319547</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>623508.433749575</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>688621.724300223</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>597588.126834607</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>648218.822495326</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>764873.217018898</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>697620.230874193</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>666114.250337429</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>660606.707335716</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>361638.114769335</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>354854.755256728</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>359334.269507701</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>398764.758849475</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>445804.528746797</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>488452.243747192</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>525686.377380415</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>576912.363274817</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>599946.331474916</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>549380.537125515</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>614121.800792383</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>691656.660011786</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>695522.703691504</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>713950.645840747</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>684812.284380378</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68664.7143876677</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65667.4406032665</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64231.6464638431</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72316.0520159425</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77711.6105254272</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90921.9742693985</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98793.5461667459</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113719.229921054</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119021.428068144</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>105058.030424561</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>103609.554211889</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>106450.926626423</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>92800.0463108607</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>94337.5814463668</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100108.014979982</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>83249.5548559727</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>80621.7920246453</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>82216.3747523335</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>87501.0282509922</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>95266.787021686</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>102302.353319841</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>109610.118357845</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>118890.160030717</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>125274.323076441</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>105745.204747566</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>109680.548434061</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>120381.317805552</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>108277.886071655</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>106717.927356406</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117918.055779261</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1401584.12705983</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1455617.59936409</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1571397.69318847</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1868690.6387404</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.944</t>
+          <t>2041751.34278143</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1978472.75810715</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>1994167.56631969</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.286</t>
+          <t>2311991.527267</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.542</t>
+          <t>2573424.65215756</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.424</t>
+          <t>2454535.9074913</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.731</t>
+          <t>2769213.59104399</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.916</t>
+          <t>2962588.45279227</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.083</t>
+          <t>3141257.20998662</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3434744.46906845</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3.817</t>
+          <t>3817222.32125563</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10.148</t>
+          <t>10536577.8057969</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.295</t>
+          <t>10666047.4179846</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10.685</t>
+          <t>11133077.0713025</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12.303</t>
+          <t>12792348.4957707</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14547573.2167109</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14.856</t>
+          <t>15592170.9314339</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15.593</t>
+          <t>16381790.6498283</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.631</t>
+          <t>18299916.0154315</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19766968.2407899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>18143192.2596062</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>19.511</t>
+          <t>20247043.6907474</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>21.017</t>
+          <t>21854162.4705849</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>22.816</t>
+          <t>23581014.9399993</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25720324.4806596</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>27.501</t>
+          <t>27500630.6795774</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32823.9930959416</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36843.1901193284</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36766.9994694645</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>43889.8782772105</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>50548.2535234676</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>59789.699437168</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>68755.8114110977</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>73897.7300231051</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>74200.7416840815</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>60073.9240422694</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>49004.9929216263</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>59631.3581596236</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>56761.6225304444</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>62822.876643545</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63438.1879323581</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>448773.75605192</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>440355.528895778</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>439194.980843175</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>488945.064996051</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>562026.668971671</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>601058.488129833</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>676744.132005296</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>759424.768713086</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>827365.570693925</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>647801.344643504</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>766074.518109491</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>883943.691163716</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>774218.51924206</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>738111.502124903</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>735502.058897783</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1440357.33313263</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1334165.98255561</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1277476.37208486</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1434459.01288642</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>1651156.23944849</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>1774555.11221426</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.197</t>
+          <t>1931743.65350128</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2124082.32656581</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>2366501.65979516</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>1816609.71393436</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.515</t>
+          <t>2094554.21685683</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2.966</t>
+          <t>2465084.09625512</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2.869</t>
+          <t>2391370.29452609</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.696</t>
+          <t>2296986.0900298</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2289878.33168544</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>567652.358198403</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>541108.734425948</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>560419.305804819</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>636032.432890234</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>755776.863138609</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>796175.831608334</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>911662.545591614</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>993730.614887613</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>1133692.63773326</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>993564.085897903</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1141241.11676684</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1399628.92622844</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1359442.30363114</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1399774.79265294</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1411569.61763451</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25857.1690138143</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24943.5486681463</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25474.1496912314</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28711.6879289369</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29801.7199835197</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32944.9912729953</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34907.6518500913</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37967.3982856051</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42923.971587214</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31495.4779700969</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33033.0388005164</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37539.5469511819</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36838.610929183</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36346.9989142802</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41871.2543135088</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3233.41122022193</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3364.42410247946</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3368.33930772088</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3890.67988715286</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4472.59554685177</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4732.38628100576</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5484.38350602527</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6371.16588726331</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>7974.91708183197</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6987.2155568653</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8780.80012918258</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8961.44709745452</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8650.15149152682</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>7502.22894099682</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7829.29611282827</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16704.0285232624</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17313.2139833202</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17630.254630949</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20148.5412920229</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21451.3313017198</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23249.5885053083</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27005.7450824333</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>29563.1136151023</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32058.9397152833</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22069.2632313742</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22259.5543638835</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>25919.9438265152</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>26427.1654781833</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>25982.2583161253</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26971.1095028251</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>632215.658695072</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>610735.615911808</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>610208.871906338</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>671045.127346358</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>773086.862652908</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>834155.573647356</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>922264.920360569</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1049909.56686336</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1142845.84642387</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>993132.782807392</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1133264.79425449</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1223292.80769507</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1228511.34074201</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1220434.40437976</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1229790.32095316</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2781.13871064921</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2492.80554410104</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2410.76586720053</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2813.3084977082</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2899.6668140058</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3133.62735126445</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3314.10994318714</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3947.8186583238</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5114.62728321588</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4114.03963252349</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4768.79928658608</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4548.8528872382</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4654.09955955861</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4474.04437411702</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4095.54756107707</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>147416.288390384</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>154897.86429834</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>160921.698773209</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>212903.460918069</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>222191.850194964</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>233370.306507685</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>249554.001619701</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>289112.534276232</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>341626.338160183</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>327918.51989183</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>372300.139614095</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>421889.665369671</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>388868.637734914</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>427745.01111434</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436158.49790188</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>287486.876728887</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>292340.243342582</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>268570.542806517</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>292232.255464435</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>329848.574196894</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>363255.098092623</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>395540.038825179</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>462468.89463989</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>528101.766727456</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>467903.515910197</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>528424.971771708</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>586710.789099479</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>555371.024102042</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>551397.536679848</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>556127.653182603</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>115024.999032304</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>112048.111509437</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>110047.097722858</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118251.024501977</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134402.778052943</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136783.129518074</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>143812.315515546</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>162118.217713726</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>177802.01064277</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>139056.641667356</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>151866.490876744</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>169663.312617242</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>152160.306514897</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>153125.382656662</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156327.551638769</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>264982.891532071</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>254629.971125379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>214676.44892031</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>239649.646051611</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>253311.423332263</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>270846.229226773</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278183.428240476</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>319371.098448553</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>339404.33234833</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>299111.428344311</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>317214.342282053</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341180.518572019</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>253602.667415379</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>250925.336152651</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>253666.164573152</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1304491.55816536</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1288158.63582166</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>1264102.92706386</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.392</t>
+          <t>1383016.25747584</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1518057.93708853</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1628563.77511991</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.702</t>
+          <t>1711153.64330836</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.923</t>
+          <t>1953622.44604868</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.963</t>
+          <t>1979981.93012441</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>1733097.70705062</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1924162.98148433</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2.031</t>
+          <t>2029178.05738609</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2024949.93160952</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.949</t>
+          <t>1921728.23735354</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>1803311.04747653</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>35338.4631684287</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>34515.1691894814</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>34182.2936287811</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>37966.2439776292</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>42747.8596582696</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>46572.9155595958</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>54100.601421746</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>64547.166788916</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>71541.3731123999</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>64235.627417805</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>66887.8813348872</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>77312.2288650105</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>74791.9281520939</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>75705.9256592698</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77550.0751938772</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16510.9527470598</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16250.517386459</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16474.6916606157</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18457.534516532</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>21991.508634676</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23215.5690883793</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25023.2453513366</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28564.829417067</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31504.6311836836</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>25941.3162789218</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>28734.8705366604</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>31557.6808159339</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28567.0802213017</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>27321.6086143509</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27976.9797011042</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>73898.8881480779</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>68859.7308296655</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67882.922621989</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>75528.6209938562</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>88424.6588822964</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>96508.5237454218</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>102153.565911515</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>115893.054506386</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>127444.572823811</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>103925.638528</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>119898.816007723</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>137118.19419754</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>128158.500374726</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>127274.853339103</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127032.989464017</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>532171.537835441</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>505545.959123278</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>481436.895902751</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>530279.588865923</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>608206.533595307</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>646160.544102737</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>664195.918956424</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>732894.587713629</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>783659.275714285</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>662729.10199628</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>824574.907116127</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>945537.388631886</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>944982.874141834</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1002149.41579391</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1109626.56681122</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>394548.412859476</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>348415.976076262</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>368898.717942572</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>426251.91354656</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>516422.507003349</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>548751.982341553</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>598665.15374457</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>672172.18759616</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>722762.724790332</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>576454.219388243</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>728732.599893296</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>812958.180368377</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>773716.862364672</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>773726.245413551</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810687.946558191</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>2143948.01719641</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>1976576.76031316</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>1969496.53211236</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2162433.79250834</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.675</t>
+          <t>2478911.40757932</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>2774576.64092702</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.237</t>
+          <t>2978018.39856208</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3.483</t>
+          <t>3169712.11544808</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.739</t>
+          <t>3394840.47807374</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>2596900.38616335</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2918057.21326584</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>3.764</t>
+          <t>3387274.88706144</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>3.695</t>
+          <t>3345168.81588278</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>3.626</t>
+          <t>3332486.01248535</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>3.444</t>
+          <t>3444191.09483201</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20.928</t>
+          <t>20871056.8044565</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21.124</t>
+          <t>21096503.5073177</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>22.628</t>
+          <t>22459393.9317825</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25.629</t>
+          <t>25469264.6359225</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>29115667.8777981</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>32.945</t>
+          <t>32729785.9828601</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>36.388</t>
+          <t>36143937.9783971</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.238</t>
+          <t>41236441.4452839</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>46.058</t>
+          <t>46247539.1568926</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>43.155</t>
+          <t>43604034.5872558</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>48173629.2755977</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>53.175</t>
+          <t>53822579.1388013</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>55.608</t>
+          <t>56577706.1169144</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>58.175</t>
+          <t>59515968.5573055</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>62.286</t>
+          <t>62285904.4752827</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>62229753.3193865</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>61.605</t>
+          <t>61604960.2125258</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>63.686</t>
+          <t>63685981.2160894</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>71.977</t>
+          <t>71977032.6483746</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>82.077</t>
+          <t>82076833.9959776</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>90.664</t>
+          <t>90663628.2520401</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>99.536</t>
+          <t>99535949.1494322</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>113.719</t>
+          <t>113719038.465387</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>126.935</t>
+          <t>126934817.736997</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>117.37</t>
+          <t>117369540.767418</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>130.256</t>
+          <t>130255885.319046</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>147.275</t>
+          <t>147274986.659704</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>151.14</t>
+          <t>151139918.668272</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>156.583</t>
+          <t>156582791.006788</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>160.997</t>
+          <t>160997197.961565</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24653.2224218151</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23838.4508962918</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24755.2824484185</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26832.6582802561</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31217.9986154087</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32739.6379797724</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35204.8534818649</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40069.4057179876</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45307.7628798201</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38433.5270866229</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>40736.0387144436</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>42805.4436704337</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39372.1371327873</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>38228.0422350248</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38091.8870205954</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>83439.0226165601</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>79420.4982949458</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>78769.3468311652</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>88199.8351867378</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>95524.8262550325</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>106334.280499828</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>117470.097158161</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>130746.047902688</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>147644.664782059</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>126557.533323748</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>135965.813485056</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>166636.924366824</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>161241.458165547</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>164071.781130501</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164162.895145874</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>35716.7304175996</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>34441.0973102351</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>34788.9906545393</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>38420.1902567357</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>43948.8044469382</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>48189.4937913885</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>51420.5575055618</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>62493.9464302253</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>68190.0621745581</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>55702.5258914399</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>61561.1144552607</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>69967.8205558838</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>69304.9525095081</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>70364.3427758508</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69973.746576493</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
